--- a/daily_matches/job_matches_2026-08-14.xlsx
+++ b/daily_matches/job_matches_2026-08-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Distinguished Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>HarbourVest</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>28.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, LLaMA, Copilot, FastAPI, Docker, Kubernetes, AKS, CI/CD</t>
+          <t>Data Scientist, RAG, Redshift, BigQuery, Data Lake, Dataflow, Apache Airflow, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab09cd891b8a55c1</t>
+          <t>https://www.indeed.com/viewjob?jk=89ec0c153166e42d</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Security Engineer</t>
+          <t>Apache Spark Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Dynanet Corporation</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>27.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Copilot, FAISS, Pinecone, Prompt Engineering, GCP Vertex AI, AKS, CI/CD</t>
+          <t>Machine Learning Engineer, RAG, S3, Glue, Synapse, Data Lake, MLflow, Docker, Kubernetes, Apache Airflow</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4a6a52a055ba853</t>
+          <t>https://www.indeed.com/viewjob?jk=86da01562515eb49</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Distinguished Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CloudBees Inc</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Kubernetes, CI/CD, Jenkins, Git, Kafka, PostgreSQL, Cassandra, NoSQL</t>
+          <t>RAG, MLflow, Snowflake, Databricks, Hadoop, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5a818a5a8c923cd</t>
+          <t>https://www.indeed.com/viewjob?jk=63201f5d771e794a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Applications Development</t>
+          <t>Sr. .NET Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AT&amp;T</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Woodlawn, MD, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, MongoDB, Cassandra, NoSQL, SQL, R</t>
+          <t>AI Engineer, RAG, Copilot, Docker, CI/CD, Terraform, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a050080ede9c5ad</t>
+          <t>https://www.indeed.com/viewjob?jk=02a522e46dc9045c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Full Stack Engineer – Architecture Team</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PurpleLab</t>
+          <t>Rethink First</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Hugging Face, spaCy, NLTK, FastAPI, Docker, CI/CD, Git, Python, SQL</t>
+          <t>Data Scientist, RAG, Docker, CI/CD, Terraform, Git, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,172 +636,172 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b0275cde50ad9bb</t>
+          <t>https://www.indeed.com/viewjob?jk=7ab5430ace02a7fb</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>PMT Engineer - Analytics and Automation</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BorgWarner</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Copilot, Kubernetes, CI/CD, Git, Kafka, Python, R</t>
+          <t>Generative AI, RAG, Copilot, Prompt Engineering, Git, Power BI, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=238c4f2407440bf5</t>
+          <t>https://www.indeed.com/viewjob?jk=7e024da6ceaebabc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior SDET--Automation Architect</t>
+          <t>Cloud Platform Engineer III</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Zions Bancorporation</t>
+          <t>University of Utah</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, SQL, R, Java</t>
+          <t>RAG, Prompt Engineering, CI/CD, GitHub Actions, Terraform, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b85aa120b725bee1</t>
+          <t>https://www.indeed.com/viewjob?jk=ac880839f17e6768</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Platform &amp; Developer Experience Engineer</t>
+          <t>Data Activation Engineer II</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Land O'Lakes</t>
+          <t>Coca-Cola Consolidated, Inc.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Arden Hills, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R</t>
+          <t>RAG, Cortex, CI/CD, Git, Snowflake, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7fc1564c41b4489</t>
+          <t>https://www.indeed.com/viewjob?jk=32ebd161a8af1725</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer II - Identity</t>
+          <t>Wi-Fi Infrastructure Test Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Berwyn, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>Generative AI, RAG, Gemini, CI/CD, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8afbc59d3f54c48c</t>
+          <t>https://www.indeed.com/viewjob?jk=ddd07401096510f5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Embedded Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Angel Studios</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, CI/CD, GitHub Actions, Git, R, Scala, Optimization</t>
+          <t>RAG, Cortex, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,147 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a79283fdf9826ee7</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Sr Software Engineer</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Angel Studios</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Provo, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>RAG, S3, Docker, Kubernetes, CI/CD, GitHub Actions, Git, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ca9d96572ffd1b24</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Senior .NET Developer – AI Technology Transformation (hybrid)</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Match Made Tech</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>10</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, LLaMA, CI/CD, Git, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d01b2b20c73ac023</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Sr DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Aspirion</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Columbus, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>10</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0862ed8a048e8750</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Sr. Artificial Intelligence &amp; Machine Learning Developer</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Ryerson</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Downers Grove, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>10</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Generative AI, Copilot, Prompt Engineering, Kubernetes, Databricks, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=658d2a2620dc619c</t>
+          <t>https://www.indeed.com/viewjob?jk=430d2baf7b548920</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-14.xlsx
+++ b/daily_matches/job_matches_2026-08-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Databricks Solution Architect - Onsite- W2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>28.9</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, BigQuery, Data Lake, Dataflow, Apache Airflow, CI/CD, GitHub Actions, Terraform</t>
+          <t>Generative AI, RAG, S3, Data Lake, MLflow, CI/CD, Terraform, Databricks, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,207 +496,207 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89ec0c153166e42d</t>
+          <t>https://www.indeed.com/viewjob?jk=c7af5960a321f1aa</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Apache Spark Developer</t>
+          <t>Java AWS Software Engineer III</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>27.8</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, S3, Glue, Synapse, Data Lake, MLflow, Docker, Kubernetes, Apache Airflow</t>
+          <t>RAG, S3, EC2, Data Lake, Docker, Kubernetes, CI/CD, Databricks, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86da01562515eb49</t>
+          <t>https://www.indeed.com/viewjob?jk=8275b35f957f4f39</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Distinguished Data Engineer</t>
+          <t>Software Engineer III - Glue/Python/Pyspark</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, MLflow, Snowflake, Databricks, Hadoop, Python, SQL, R, Java, Scala</t>
+          <t>RAG, S3, Glue, CI/CD, Terraform, PySpark, Kafka, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63201f5d771e794a</t>
+          <t>https://www.indeed.com/viewjob?jk=c6b0adf7ee0ca945</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr. .NET Developer</t>
+          <t>BizAI Tech Functional Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Woodlawn, MD, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Docker, CI/CD, Terraform, PostgreSQL, Python, SQL, R</t>
+          <t>AI Engineer, FastAPI, Docker, Kubernetes, Databricks, PostgreSQL, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02a522e46dc9045c</t>
+          <t>https://www.indeed.com/viewjob?jk=f60201cb1ca5b892</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer – Architecture Team</t>
+          <t>Java Software Engineer II</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Rethink First</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, CI/CD, Terraform, Git, SQL, R, Java, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ab5430ace02a7fb</t>
+          <t>https://www.indeed.com/viewjob?jk=46a2d5bdb0ace6e8</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PMT Engineer - Analytics and Automation</t>
+          <t>AI PLATFORM ENGINEER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BorgWarner</t>
+          <t>Acuhuman</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Prompt Engineering, Git, Power BI, Python, SQL, R, Optimization</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Copilot, Kubernetes, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e024da6ceaebabc</t>
+          <t>https://www.indeed.com/viewjob?jk=682a8152cd81abc9</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer III</t>
+          <t>DEVOPS ENGINEER</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, CI/CD, GitHub Actions, Terraform, Git, Python, R, Java, Scala</t>
+          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac880839f17e6768</t>
+          <t>https://www.indeed.com/viewjob?jk=7c3c253f639a5638</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Activation Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Coca-Cola Consolidated, Inc.</t>
+          <t>Smart Apply Test Company</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Cortex, CI/CD, Git, Snowflake, Python, SQL, R, Optimization</t>
+          <t>Data Scientist, Hugging Face, spaCy, NLTK, FastAPI, Docker, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32ebd161a8af1725</t>
+          <t>https://www.indeed.com/viewjob?jk=5b7fa44f49ac8d1e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Wi-Fi Infrastructure Test Engineer</t>
+          <t>Sr.  Backend Engineer - Core Infrastructure</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Berwyn, IL, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, Git, Python, R, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, MongoDB, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddd07401096510f5</t>
+          <t>https://www.indeed.com/viewjob?jk=fab49072e1b15fef</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Embedded Software Engineer</t>
+          <t>Data Warehouse Software Engineer III</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Babel Street</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,17 +801,192 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Cortex, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Optimization</t>
+          <t>RAG, BigQuery, Apache Airflow, CI/CD, Git, BigQuery, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e34dd82bc09fa105</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SENIOR AI ENGINEER</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Coforge</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Oaks, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, CI/CD, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2225bd72008b1911</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Senior Agentic Automations Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Qualcomm</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Docker, Kubernetes, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2ba5d6c1202e290b</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Java Software Engineer III</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Cassandra, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=156e57fe462d4979</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Data Engineer - Finance AI Solutions</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Brooklyn Park, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, PySpark, Hadoop, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=430d2baf7b548920</t>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1f6056b3749eea65</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Data Scientist (PGC) - TikTok</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, RAG, Python, SQL, R, Optimization, Hypothesis Testing, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d1960bcfaf9fdcbe</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-14.xlsx
+++ b/daily_matches/job_matches_2026-08-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Modeling &amp; AI Analytics</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Redapt inc</t>
+          <t>Matrix International Financial Services</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, GitHub Actions, Terraform, Git, Python, R, Java, Scala</t>
+          <t>RAG, Redshift, BigQuery, Git, Snowflake, BigQuery, Redshift, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,7 +496,252 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a192e93f96c7fb3d</t>
+          <t>https://www.indeed.com/viewjob?jk=da0b9d9f202b441a</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Customer Reliability Engineer - Airflow</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Astronomer</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Boston, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, Docker, Kubernetes, Apache Airflow, Snowflake, Databricks, Redshift, PostgreSQL, Python</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e441a087ab697b63</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>American Fidelity Assurance Company</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Oklahoma City, OK, US USA</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Data Scientist, TensorFlow, Hadoop, Tableau, Power BI, Python, SQL, R, Java, Julia</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2c6c39c21e46ffed</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Data Scientist - San Juan PR</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>San Juan, PR, US USA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, TensorFlow, PyTorch, XGBoost, Azure ML, MLflow, Power BI, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=30616f08af993330</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Senior Informatics Engineer</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Eikon Therapeutics</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Millbrae, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Docker, Git, Databricks, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=caddb12f09513052</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Software Architect, Back-End</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>TED Conferences</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Git, MySQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=91f724816f0e7d8f</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer (Contract)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Hillsborough County Clerk of Court &amp; Comptroller</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Kubernetes, Terraform, Git, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6acdc3c6089d3de0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Domain Consultant 2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Palo Alto Networks</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Prompt Engineering, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=77e8c59213bb9446</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-14.xlsx
+++ b/daily_matches/job_matches_2026-08-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Modeling &amp; AI Analytics</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Matrix International Financial Services</t>
+          <t>Campbell's</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13.3</v>
+        <v>25.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Git, Snowflake, BigQuery, Redshift, Tableau, Python, SQL</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, XGBoost, LightGBM, Synapse, MLflow, Docker, AKS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da0b9d9f202b441a</t>
+          <t>https://www.indeed.com/viewjob?jk=6b48d41859a14d7e</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Customer Reliability Engineer - Airflow</t>
+          <t>Data Architect-68464</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>Hitachi Rail</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Boston, NY, US USA</t>
+          <t>Reading, PA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.3</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Redshift, Docker, Kubernetes, Apache Airflow, Snowflake, Databricks, Redshift, PostgreSQL, Python</t>
+          <t>RAG, S3, Glue, Redshift, Data Lake, Docker, Kubernetes, CI/CD, Git, Snowflake</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e441a087ab697b63</t>
+          <t>https://www.indeed.com/viewjob?jk=9d634d7b84760169</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior AI Engineer I - Global Dining</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>American Fidelity Assurance Company</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, Hadoop, Tableau, Power BI, Python, SQL, R, Java, Julia</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c6c39c21e46ffed</t>
+          <t>https://www.indeed.com/viewjob?jk=891a966c96f6d006</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Scientist - San Juan PR</t>
+          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, TensorFlow, PyTorch, XGBoost, Azure ML, MLflow, Power BI, Python, SQL</t>
+          <t>RAG, Data Lake, Snowflake, Databricks, PySpark, Kafka, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30616f08af993330</t>
+          <t>https://www.indeed.com/viewjob?jk=8bb89514a86b7c54</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Informatics Engineer</t>
+          <t>Senior AI ML Engineer - Remote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Eikon Therapeutics</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Millbrae, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Docker, Git, Databricks, Python, SQL, R, Java, Scala</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Git, PostgreSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caddb12f09513052</t>
+          <t>https://www.indeed.com/viewjob?jk=e2526a42c3133b45</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Architect, Back-End</t>
+          <t>Software Engineer I (MERN, AWS)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TED Conferences</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Git, MySQL, SQL, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91f724816f0e7d8f</t>
+          <t>https://www.indeed.com/viewjob?jk=891a85e16c3fc393</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Contract)</t>
+          <t>Information Systems Engineer - NOC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Hillsborough County Clerk of Court &amp; Comptroller</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Kubernetes, Terraform, Git, Python, SQL, R, Scala</t>
+          <t>RAG, S3, EC2, Kubernetes, Jenkins, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6acdc3c6089d3de0</t>
+          <t>https://www.indeed.com/viewjob?jk=a40541a4b1708cab</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Domain Consultant 2</t>
+          <t>Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>Landmark Properties, Inc.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Athens, GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Prompt Engineering, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
+          <t>Dataflow, CI/CD, Git, PySpark, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,112 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77e8c59213bb9446</t>
+          <t>https://www.indeed.com/viewjob?jk=6ed1ad8a3c88baae</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Microsoft Fabric Data Engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Landmark Properties, Inc.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Dataflow, CI/CD, Git, PySpark, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f5b4d249126be9c1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Applied Scientist</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Adobe</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Prompt Engineering, Git, Databricks, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=89cae7386c9ffef2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Forward Deployed Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Vitol</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=68753e681a324861</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-14.xlsx
+++ b/daily_matches/job_matches_2026-08-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Architect-68464</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Campbell's</t>
+          <t>Hitachi Energy</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Reading, PA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>25.6</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, XGBoost, LightGBM, Synapse, MLflow, Docker, AKS</t>
+          <t>RAG, S3, Glue, Redshift, Data Lake, Docker, Kubernetes, CI/CD, Git, Snowflake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b48d41859a14d7e</t>
+          <t>https://www.indeed.com/viewjob?jk=f8c2a6ef929081a1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Architect-68464</t>
+          <t>AI Developer/Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hitachi Rail</t>
+          <t>Delaware Nation Industries</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Reading, PA, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Redshift, Data Lake, Docker, Kubernetes, CI/CD, Git, Snowflake</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d634d7b84760169</t>
+          <t>https://www.indeed.com/viewjob?jk=ec646ad9372dc2a6</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior AI Engineer I - Global Dining</t>
+          <t>DATA ENGINEER I</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka</t>
+          <t>Data Scientist, RAG, Prompt Engineering, Redshift, BigQuery, Synapse, Git, Snowflake, BigQuery, Redshift</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=891a966c96f6d006</t>
+          <t>https://www.indeed.com/viewjob?jk=e8092db12dbdd54c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Snowflake, Databricks, PySpark, Kafka, NoSQL, Python, SQL, R</t>
+          <t>RAG, Gemini, Copilot, S3, EC2, Docker, Kubernetes, CI/CD, Terraform, MySQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bb89514a86b7c54</t>
+          <t>https://www.indeed.com/viewjob?jk=ba2bc4f8478f2f52</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior AI ML Engineer - Remote</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Delaware Nation Industries</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Git, PostgreSQL, Python, SQL, R, Scala</t>
+          <t>Generative AI, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, MySQL, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2526a42c3133b45</t>
+          <t>https://www.indeed.com/viewjob?jk=186e1b06b60d4c75</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer I (MERN, AWS)</t>
+          <t>Senior Data Engineer - AI Infrastructure Integration, High Performance Compute</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java, Scala, Optimization</t>
+          <t>Generative AI, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, spaCy, Gensim, CI/CD, Tableau, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=891a85e16c3fc393</t>
+          <t>https://www.indeed.com/viewjob?jk=5241e6d3afdd79e3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Information Systems Engineer - NOC</t>
+          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Kubernetes, Jenkins, Terraform, Git, Python, R</t>
+          <t>AI Engineer, Generative AI, RAG, Docker, Kubernetes, CI/CD, Git, Snowflake, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a40541a4b1708cab</t>
+          <t>https://www.indeed.com/viewjob?jk=9d7b0c0663856b10</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Landmark Properties, Inc.</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Athens, GA, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dataflow, CI/CD, Git, PySpark, Power BI, Python, SQL, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, PostgreSQL, MySQL, MongoDB, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ed1ad8a3c88baae</t>
+          <t>https://www.indeed.com/viewjob?jk=32d403b17a686b11</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Data Engineer</t>
+          <t>Senior Specialty Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Landmark Properties, Inc.</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dataflow, CI/CD, Git, PySpark, Power BI, Python, SQL, R, Scala</t>
+          <t>Generative AI, RAG, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Git, R, Java</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5b4d249126be9c1</t>
+          <t>https://www.indeed.com/viewjob?jk=5a166a8f088f0c0c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Applied Scientist</t>
+          <t>Senior Specialty Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, Git, Databricks, Python, R, Scala, Optimization</t>
+          <t>Generative AI, RAG, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Git, R, Java</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,42 +811,252 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89cae7386c9ffef2</t>
+          <t>https://www.indeed.com/viewjob?jk=883e65697cefb749</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Senior Software Engineer, Full-Stack</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Vitol</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RAG, S3, CI/CD, MySQL, MongoDB, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7a883098a725d899</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Scientific Technical Engineer - PDS&amp;T CMC</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>AbbVie</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>North Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Glue, CI/CD, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=097744a388fc20c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Backend Engineering</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Caterpillar</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Git, PostgreSQL, MySQL, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=764eaa8799f2fbba</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>AI Technical Consultant</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Copilot, Prompt Engineering, Git, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bf232f88bd55a1a9</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Software Engineer IV</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Acima Leasing</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Draper, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
         <v>10</v>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, Python, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=68753e681a324861</t>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=85a461cbdd0e503a</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Observability &amp; SRE Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>World Wide Technology</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f62f2aa3a1c8ddb2</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>AIML Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Alpharetta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=34723ca211ba48e8</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-14.xlsx
+++ b/daily_matches/job_matches_2026-08-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Architect-68464</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Hitachi Energy</t>
+          <t>Nestlé Purina</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Reading, PA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Redshift, Data Lake, Docker, Kubernetes, CI/CD, Git, Snowflake</t>
+          <t>Data Scientist, LangChain, RAG, Copilot, Prompt Engineering, Azure ML, MLflow, Git, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8c2a6ef929081a1</t>
+          <t>https://www.indeed.com/viewjob?jk=2f94258f281c4987</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Developer/Engineer</t>
+          <t>Senior Software Engineer (API Integrations)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Delaware Nation Industries</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Davie, FL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD</t>
+          <t>RAG, Copilot, S3, Kinesis, Docker, CI/CD, GitHub Actions, Git, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec646ad9372dc2a6</t>
+          <t>https://www.indeed.com/viewjob?jk=4473ab579b8e449a</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DATA ENGINEER I</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Prompt Engineering, Redshift, BigQuery, Synapse, Git, Snowflake, BigQuery, Redshift</t>
+          <t>Generative AI, LangChain, RAG, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8092db12dbdd54c</t>
+          <t>https://www.indeed.com/viewjob?jk=3a7b080695582692</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Senior Cloud Engineering Architect - Evinova</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ISPOT</t>
+          <t>AstraZeneca</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Gaithersburg, MD, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Copilot, S3, EC2, Docker, Kubernetes, CI/CD, Terraform, MySQL</t>
+          <t>RAG, S3, EC2, Glue, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba2bc4f8478f2f52</t>
+          <t>https://www.indeed.com/viewjob?jk=0f4e06659b43811d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Expert Data Scientist</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Delaware Nation Industries</t>
+          <t>Nestlé Purina</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, MySQL, Python, SQL</t>
+          <t>Data Scientist, Generative AI, RAG, Copilot, TensorFlow, Git, Hadoop, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=186e1b06b60d4c75</t>
+          <t>https://www.indeed.com/viewjob?jk=45cd5ea2ca8ed88e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - AI Infrastructure Integration, High Performance Compute</t>
+          <t>AEM Developer with Java</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>merican Inc</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>11.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, spaCy, Gensim, CI/CD, Tableau, Python</t>
+          <t>RAG, Copilot, S3, CI/CD, Jenkins, GitHub Actions, Git, R, Java, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5241e6d3afdd79e3</t>
+          <t>https://www.indeed.com/viewjob?jk=84e4d7aec84d13b5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
+          <t>AI Enablement Intern</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>CCC Intelligent Solutions</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Docker, Kubernetes, CI/CD, Git, Snowflake, Python, SQL</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, Kubernetes, Terraform, Git, Python, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d7b0c0663856b10</t>
+          <t>https://www.indeed.com/viewjob?jk=b2db5653723f53cb</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Associate Software Engineer - Java (Distributed Systems and Databases)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>New Relic</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, PostgreSQL, MySQL, MongoDB, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, Git, MySQL, MongoDB, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32d403b17a686b11</t>
+          <t>https://www.indeed.com/viewjob?jk=eba4a94f26ebfc6f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Specialty Software Engineer</t>
+          <t>Finance Systems Engineer, Finance and Strategy</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Git, R, Java</t>
+          <t>RAG, BigQuery, Dataflow, Git, BigQuery, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a166a8f088f0c0c</t>
+          <t>https://www.indeed.com/viewjob?jk=aec5b7dcc5fa2fb5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Specialty Software Engineer</t>
+          <t>Sr. Data Analyst I</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Reserv</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Git, R, Java</t>
+          <t>RAG, BigQuery, Git, Snowflake, BigQuery, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=883e65697cefb749</t>
+          <t>https://www.indeed.com/viewjob?jk=2f1bec9dbdc6fcfd</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Full-Stack</t>
+          <t>Software Developer Intern</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Ericsson</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,42 +836,42 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, S3, CI/CD, MySQL, MongoDB, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Python, R, Java</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a883098a725d899</t>
+          <t>https://www.indeed.com/viewjob?jk=f65be63ea11c23cf</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Scientific Technical Engineer - PDS&amp;T CMC</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Flex</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>North Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Glue, CI/CD, Snowflake, Databricks, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, CI/CD, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=097744a388fc20c6</t>
+          <t>https://www.indeed.com/viewjob?jk=aeffe0390be7d3a0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Backend Engineering</t>
+          <t>Senior Software Engineer, Apps &amp; Behaviors</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>SmartThings</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, PostgreSQL, MySQL, NoSQL, SQL, R, Java, Scala</t>
+          <t>RAG, EC2, Kinesis, Terraform, MySQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=764eaa8799f2fbba</t>
+          <t>https://www.indeed.com/viewjob?jk=caea69b877e2e76a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI Technical Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Crowe</t>
+          <t>Epik Solutions</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Prompt Engineering, Git, Python, SQL, R, Java, Scala</t>
+          <t>Gemini, BigQuery, Dataflow, CI/CD, BigQuery, PySpark, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf232f88bd55a1a9</t>
+          <t>https://www.indeed.com/viewjob?jk=8e89baba9f63a95f</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer IV</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Acima Leasing</t>
+          <t>Crowe</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, Python, R, Java, Scala, Optimization</t>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85a461cbdd0e503a</t>
+          <t>https://www.indeed.com/viewjob?jk=669f0d85ebd0d235</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Observability &amp; SRE Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>World Wide Technology</t>
+          <t>Crowe</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f62f2aa3a1c8ddb2</t>
+          <t>https://www.indeed.com/viewjob?jk=b30a9e591aca24c3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AIML Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Crowe</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, Python, R, Java</t>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,1407 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34723ca211ba48e8</t>
+          <t>https://www.indeed.com/viewjob?jk=7f6cd73189dc9c8d</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eee7c9308999761f</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=360cfde9cf0f2d84</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>The Woodlands, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=760ef15179ee9ff1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Lexington, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=27f96e417b5ae26d</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c225d220e1af0099</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4c27c5925acf8e6d</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b3987c45150f6d09</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Springfield, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5594c0cf54496c04</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Fort Wayne, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=438aa437ba02ed62</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Oakbrook Terrace, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a80bfd707b6f21a6</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=116fb3c2446591a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f6a502f055c26ed0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ede98915c959ce4a</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Boca Raton, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cb71ea2862851eb4</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=07dd924124ee215e</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cfeb36740cc281e0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Livingston, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ccf066da75118f1c</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ecd2689c7afb058c</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Grand Rapids, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=34dcd81c2045de86</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f5ffd6c2c37a2114</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=88b250b8b62ff8a4</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a7d295d748511d3d</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Knoxville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=48616e20df248ab6</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>South Bend, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ca3f57446cf6cebe</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=af5d80c12e0e3c60</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>10</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c452ff99e8bcaa6c</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Tallahassee, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1ffdd91a44f91c60</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dac2ea23f2c910ed</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b288672c7f312970</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1cc0f9fe61d6a990</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Burlington, VT, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>10</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b78373d0b07c5329</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>10</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ab03d604858d549e</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Costa Mesa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>10</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ba01131b78669172</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Sarasota, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>10</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5ef899f6639ba40f</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Slate Auto</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>10</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>RAG, S3, Glue, Redshift, Redshift, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=812be7ff2c58a8e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Samsung Electronics</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Taylor, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>10</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, XGBoost, PySpark, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9900d8d44dc98197</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Recommendations</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Klaviyo</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>10</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Kubernetes, CI/CD, Git, MySQL, NoSQL, Python, SQL, R, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e596dfb10c9eeb52</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Data / AI Architect</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Cloud and Things</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>10</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Synapse, Git, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bfc2692c1cf38a3f</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>The Coca-Cola Company</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Python, SQL, R, Optimization, Bayesian, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8f0a5ab32861a1d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence Engineer I</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Insperity</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Kingwood, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>10</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, Git, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6be916b5150c987a</t>
         </is>
       </c>
     </row>
